--- a/output/2026-10-08_02_Serbia_Kolubarski_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-08_02_Serbia_Kolubarski_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -478,7 +478,6 @@
           <t>VAMAG Valjevo</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Valjevo, Kolubarski okrug</t>
@@ -494,10 +493,9 @@
           <t>062/415-906</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Esistenza confermata su directory PlanPlus (Radnička 3, Valjevo), categoria 'Construction Machines and Tools'. Nessun sito web ufficiale reperito. Attivita adiacente al metalworking ma non specifica (macchine edili/utensili generici).</t>
+          <t>Esistenza confermata su directory PlanPlus (Radnička 3, Valjevo), categoria 'Construction Machines and Tools'. Nessun sito web ufficiale reperito. Attivita adiacente al metalworking ma non specifica (macchine edili/utensili generici). [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,7 +552,6 @@
           <t>Woby Haus - prodaja mašina i alata</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Valjevo, Kolubarski okrug</t>
@@ -570,10 +567,9 @@
           <t>014/230-121</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Esistenza confermata su directory PlanPlus (Uzun Mirkova 2B, Valjevo, presso retail park STOP SHOP). Nessun sito web ufficiale reperito, nessuna email trovata.</t>
+          <t>Esistenza confermata su directory PlanPlus (Uzun Mirkova 2B, Valjevo, presso retail park STOP SHOP). Nessun sito web ufficiale reperito, nessuna email trovata. [DUPLICATO — vedi anche: 2026-10-08_01_Serbia_Kolubarski_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -588,7 +584,6 @@
           <t>Sinbo DOO Lazarevac (punto vendita Lajkovac) - STIHL prodaja</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Lajkovac, Kolubarski okrug (sede legale Lazarevac)</t>
@@ -604,7 +599,6 @@
           <t>014/343-3533</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Confermato tramite profilo eKapija: PRIVREDNO DRUSTVO ZA UNUTRASNJU I SPOLJNU TRGOVINU SINBO DOO LAZAREVAC, nata come officina elettromeccanica nel 1967, partner ufficiale STIHL dal 2015, punto vendita a Lajkovac aperto dal 2006. Nessun sito web proprio reperito.</t>

--- a/output/2026-10-08_02_Serbia_Kolubarski_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-08_02_Serbia_Kolubarski_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (12/10/2026)</t>
         </is>
       </c>
     </row>
